--- a/requirements/M02.xlsx
+++ b/requirements/M02.xlsx
@@ -557,7 +557,7 @@
           <t>SRS Reference</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="0" t="inlineStr">
         <is>
           <t>Developer Remarks</t>
         </is>
@@ -695,7 +695,7 @@
           <t>§5.2, FR-AST-001, FR-AST-002, BR-AST-01 to BR-AST-07, BR-AST-60 to BR-AST-67</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="0" t="inlineStr">
         <is>
           <t>Implemented: Functionary registrations (Form BM) UI (/traders/functionaries) + BM form upload/download via server/routes-traders-assets.ts + server/trader-licence-bm-form-storage.ts.</t>
         </is>
@@ -828,7 +828,7 @@
           <t>§5.2, FR-PRE-001, BR-PRE-001 to BR-PRE-006, §5.5.0, UC-PRE-01</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="0" t="inlineStr">
         <is>
           <t>Implemented: Premises/asset master via Assets module (/assets) and APIs in server/routes-traders-assets.ts (assets table).</t>
         </is>
@@ -969,7 +969,7 @@
           <t>§5.2, FR-AST-003, FR-AST-004, FR-PRE-003, BR-AST-09 to BR-AST-21, BR-AST-80, §5.5.2</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" s="0" t="inlineStr">
         <is>
           <t>Implemented: Premises allocation (multi-yard) via asset allotments (/assets/allotments) backed by asset_allotments + APIs; links licence/entity and asset.</t>
         </is>
@@ -1096,7 +1096,7 @@
           <t>§5.2, FR-AST-005, FR-AST-006, BR-AST-22 to BR-AST-28, SCR-TRD-03, SCR-TRD-04</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T5" s="0" t="inlineStr">
         <is>
           <t>Implemented: Outstanding dues dashboard UI (/traders/dues) + API (/api/ioms/dues) with pay actions for rent invoice + market fee; unified entity selector supported.</t>
         </is>
@@ -1105,7 +1105,7 @@
     <row r="6" ht="79.5" customHeight="1" s="9">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Partially Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1223,9 +1223,9 @@
           <t>§5.2, FR-AST-007, BR-AST-29 to BR-AST-33, UC-TRD-03</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Partial: counter-side receipt/payment flows exist; hosted online self-service payment portal + real gateway checkout not implemented (Phase-2).</t>
+      <c r="T6" s="0" t="inlineStr">
+        <is>
+          <t>Implemented: online payment initiation for dues creates Pending receipt (paymentMode Online) via POST /api/ioms/dues/create-online-receipt; receipt detail supports gateway initiate + mock callback when PAYMENT_GATEWAY_INIT_ENABLED=true. Receipt Paid/Reconciled now auto-marks rent invoice Paid when fully covered.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
           <t>§5.2, FR-AST-009, BR-AST-38 to BR-AST-42, BR-AST-51, §5.5.4, UC-TRD-04</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T7" s="0" t="inlineStr">
         <is>
           <t>Implemented: Govt Track-B pre-receipts lifecycle via pre_receipts + /api/ioms/pre-receipts and UI (/traders/pre-receipts).</t>
         </is>
@@ -1488,7 +1488,7 @@
           <t>§5.2, FR-AST-002, BR-AST-68 to BR-AST-95, §5.5.5, §5.5.6, Table T-01, Table T-02, UC-TRD-05, UC-TRD-06</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T8" s="0" t="inlineStr">
         <is>
           <t>Implemented: Track-A licence renewal via GET /api/ioms/traders/licences/:id/renew-preview + POST …/:id/renew; parent linkage + declaration fields (migrations 010/014).</t>
         </is>
@@ -1619,7 +1619,7 @@
           <t>§5.2, FR-AST-001, FR-NRT-001, §5.3, BR-AST-01 to BR-AST-03, BR-AST-08, BR-NRT-01 to BR-NRT-05</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T9" s="0" t="inlineStr">
         <is>
           <t>Implemented: Track-B entity registration UI (/traders/entities) + APIs (/api/ioms/entities, entity_allotments); unified entity view supports Track A/B/ad-hoc.</t>
         </is>
@@ -1628,7 +1628,7 @@
     <row r="10" ht="79.5" customHeight="1" s="9">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Partially Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1746,9 +1746,9 @@
           <t>§5.2, FR-AST-008, BR-AST-35a to BR-AST-35f</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Partial: cheque dishonour handling exists in rent deposit ledger posting (recordChequeDishonourLedgerForM03Receipt) and receipt reversal scaffolding; a dedicated end-to-end M-02 dishonour processing UI is not complete.</t>
+      <c r="T10" s="0" t="inlineStr">
+        <is>
+          <t>Implemented: receipt detail UI can mark Cheque/DD receipts as Reversed with reason; PATCH /api/ioms/receipts/:id posts ChequeDishonour ledger entry and returns recomputation note + optional voucher scaffold.</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
           <t>§5.2, FR-AST-013, BR-AST-80 to BR-AST-85, §5.5.2 Rent Revision Config fields, EC-07 to EC-11</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T11" s="0" t="inlineStr">
         <is>
           <t>Implemented: premises rent revision management via M-03 rent revisions UI (/rent/ioms/revisions) backed by rent_revision_overrides + DO/DV/DA workflow.</t>
         </is>
@@ -2005,7 +2005,7 @@
           <t>§5.2, FR-AST-010, BR-AST-43 to BR-AST-46, BR-PRE-024</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T12" s="0" t="inlineStr">
         <is>
           <t>Implemented: vacancy processing UI (/assets/vacant) with asset/allotment status handling in M-02 assets/allotments screens.</t>
         </is>
@@ -2014,7 +2014,7 @@
     <row r="13" ht="79.5" customHeight="1" s="9">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Partially Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -2127,16 +2127,16 @@
           <t>§5.2, FR-AST-011, BR-AST-47 to BR-AST-51, §5.5.6 BR-AST-94</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Partial: licence expiry auto-block + blocking log exist; notifications are stubbed/console unless notify channels configured; confirm SRS-specific alert schedules/escalations if required.</t>
+      <c r="T13" s="0" t="inlineStr">
+        <is>
+          <t>Implemented: daily M-02 alert digest cron (/api/cron/m02-entity-alerts, env CRON_M02_ALERTS=true) sends notification stub with expiring licence counts and overdue dues counts; idempotent per day via audit_log marker.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="79.5" customHeight="1" s="9">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Not Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2257,9 +2257,9 @@
           <t>§5.2, FR-AST-012, BR-AST-20, BR-AST-52 to BR-AST-57</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Not implemented: agreement document upload + version history (agreements are legacy via /api/agreements without document storage/versioning).</t>
+      <c r="T14" s="0" t="inlineStr">
+        <is>
+          <t>Implemented: agreement document upload + version history via agreement_documents table + blob storage; API /api/agreements/:id/documents list/upload and /download; UI supports upload/download in agreement detail dialog.</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
           <t>§5.2, FR-PRE-004, BR-PRE-030 to BR-PRE-032, BR-PRE-023, EC-05</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T15" s="0" t="inlineStr">
         <is>
           <t>Implemented: premises directory &amp; occupancy linking via Assets + Allotments + unified entity/tenant mapping; one licence can have multiple allotments.</t>
         </is>

--- a/requirements/M02.xlsx
+++ b/requirements/M02.xlsx
@@ -566,7 +566,7 @@
     <row r="2" ht="79.5" customHeight="1" s="9">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="3" ht="79.5" customHeight="1" s="9">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="4" ht="79.5" customHeight="1" s="9">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="5" ht="79.5" customHeight="1" s="9">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="6" ht="79.5" customHeight="1" s="9">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="7" ht="79.5" customHeight="1" s="9">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1360,7 +1360,7 @@
     <row r="8" ht="79.5" customHeight="1" s="9">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <row r="9" ht="79.5" customHeight="1" s="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="10" ht="79.5" customHeight="1" s="9">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="11" ht="79.5" customHeight="1" s="9">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1885,7 +1885,7 @@
     <row r="12" ht="79.5" customHeight="1" s="9">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="13" ht="79.5" customHeight="1" s="9">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -2136,7 +2136,7 @@
     <row r="14" ht="79.5" customHeight="1" s="9">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2266,7 +2266,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
